--- a/Result/profitability/3010.xlsx
+++ b/Result/profitability/3010.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.41</v>
       </c>
       <c r="M2" t="n">
-        <v>2.19375</v>
+        <v>2.2825</v>
       </c>
       <c r="N2" t="n">
-        <v>8.5525</v>
+        <v>8.64875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>1.03</v>
       </c>
       <c r="M3" t="n">
-        <v>1.97875</v>
+        <v>2.15125</v>
       </c>
       <c r="N3" t="n">
-        <v>9.07</v>
+        <v>9.1775</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>1.45</v>
       </c>
       <c r="M4" t="n">
-        <v>1.9</v>
+        <v>2.09</v>
       </c>
       <c r="N4" t="n">
-        <v>9.892500000000002</v>
+        <v>10</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.57</v>
       </c>
       <c r="M5" t="n">
-        <v>1.58625</v>
+        <v>1.8125</v>
       </c>
       <c r="N5" t="n">
-        <v>10.21</v>
+        <v>10.2825</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.3</v>
       </c>
       <c r="M6" t="n">
-        <v>1.4175</v>
+        <v>1.51375</v>
       </c>
       <c r="N6" t="n">
-        <v>10.6975</v>
+        <v>10.7075</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,13 +1264,13 @@
         <v>1.12</v>
       </c>
       <c r="M7" t="n">
-        <v>1.22125</v>
+        <v>1.33375</v>
       </c>
       <c r="N7" t="n">
-        <v>11.18375</v>
+        <v>11.13</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>1.23</v>
       </c>
       <c r="M8" t="n">
-        <v>1.055</v>
+        <v>1.17875</v>
       </c>
       <c r="N8" t="n">
-        <v>11.5625</v>
+        <v>11.5875</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3010</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>23841</v>
+      </c>
+      <c r="D75" t="n">
+        <v>21853</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1988</v>
+      </c>
+      <c r="F75" t="n">
+        <v>8.34</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1010</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>4.24%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>281</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1291</v>
+      </c>
+      <c r="K75" t="n">
+        <v>898</v>
+      </c>
+      <c r="L75" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="M75" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="N75" t="n">
+        <v>7.975000000000001</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.9899999999999998</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.4008097165991902</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.1999999999999993</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.02457002457002444</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.096969696969697</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0.5800000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.07474226804123707</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
